--- a/サーバー状況.xlsx
+++ b/サーバー状況.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\黒い砂漠mobile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\黒い砂漠mobile\税収計算Web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260AB41C-F6FA-41F5-A855-33F6AEE1A63B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACB6F78-EA82-4C14-B354-FEC829BF1818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{248E318C-A0FD-4EA4-9016-A8AF9321EC7A}"/>
+    <workbookView xWindow="-26550" yWindow="1680" windowWidth="19680" windowHeight="11985" xr2:uid="{248E318C-A0FD-4EA4-9016-A8AF9321EC7A}"/>
   </bookViews>
   <sheets>
     <sheet name="AM" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="67">
   <si>
     <t>WR</t>
     <phoneticPr fontId="1"/>
@@ -695,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EA3A10D-D83F-4A84-A525-60830EF0D854}">
-  <dimension ref="B3:F44"/>
+  <dimension ref="B3:F45"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4.125" customWidth="1"/>
@@ -1177,6 +1177,11 @@
     <row r="44" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B45" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1672,7 +1677,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A289003-7013-42EF-B7E6-8D82A34C3917}">
-  <dimension ref="B3:F44"/>
+  <dimension ref="B3:F45"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4.125" customWidth="1"/>
@@ -2156,6 +2161,11 @@
         <v>56</v>
       </c>
     </row>
+    <row r="45" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B45" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
